--- a/docs/07_API一覧.xlsx
+++ b/docs/07_API一覧.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用例" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API一覧'!$A$1:$L$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API一覧'!$A$1:$L$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -639,7 +639,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -658,24 +658,36 @@
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>関連文書</t>
+          <t>更新日</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>詳細設計書（ZCN-DD-001）</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>関連文書</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>詳細設計書（ZCN-DD-001）/ OpenAPI（apps/api/openapi.yaml）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>API総数</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>13件（Query 5, Mutation 5, REST 3）</t>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>16件（GraphQL Query 5, GraphQL Mutation 5, REST 6）</t>
         </is>
       </c>
     </row>
@@ -839,7 +851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1699,8 +1711,188 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="75" customHeight="1">
+      <c r="A15" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Swagger UI</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>/docs</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>HTML（Swagger UI）</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>—（API ドキュメント閲覧）</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>swagger-ui-express による OpenAPI 3.1 ベースのドキュメントUI。「Try it out」で実APIを叩ける。openapi.yaml の servers 先頭が url:/ のため、Try it out 時のリクエストは同一オリジンになり CORS の影響を受けない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="75" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>OpenAPI YAML</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>/openapi.yaml</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>text/yaml</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 仕様（YAML形式）。Postman / Insomnia / OpenAPI Generator などにインポートする際の入力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="75" customHeight="1">
+      <c r="A17" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>OpenAPI JSON</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>/openapi.json</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>application/json</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 仕様（JSON形式）。CI / コード生成ツールでの利用。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L14"/>
+  <autoFilter ref="A1:L17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2218,7 +2410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2499,15 +2691,73 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+    <row r="17" ht="100" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>[REST] Swagger UI
+GET /docs</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>GET /docs</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>HTTP/1.1 200 OK
+Content-Type: text/html
+(Swagger UI HTML)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="100" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>[REST] OpenAPI YAML
+GET /openapi.yaml</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>GET /openapi.yaml</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>openapi: 3.1.0
+info: ...
+(略)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="100" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>[REST] OpenAPI JSON
+GET /openapi.json</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>GET /openapi.json</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>{ "openapi": "3.1.0", "info": {...}, ... }</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>認証 Cookie の取得方法（curl 例）</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="180" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
+    <row r="23" ht="180" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve"># 1. ログインしてCookieを保存
 curl -i -c cookies.txt -X POST http://localhost:4000/graphql \
@@ -2522,13 +2772,13 @@
 </t>
         </is>
       </c>
-      <c r="B20" s="21" t="n"/>
-      <c r="C20" s="22" t="n"/>
+      <c r="B23" s="21" t="n"/>
+      <c r="C23" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A23:C23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
